--- a/dataset_t6_grouped/results2/G0/G0_DMSO_W0082F0002T0006Z000C1N111_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G0/G0_DMSO_W0082F0002T0006Z000C1N111_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>49.48733636670952</v>
+        <v>8.041692159590298</v>
       </c>
       <c r="D2" t="n">
-        <v>49.51948682999417</v>
+        <v>8.046916609874053</v>
       </c>
       <c r="E2" t="n">
-        <v>18.01756697769656</v>
+        <v>2.927854633875691</v>
       </c>
       <c r="F2" t="n">
-        <v>17.97150031956095</v>
+        <v>2.920368801928654</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>93.94576326974524</v>
+        <v>15.2661865313336</v>
       </c>
       <c r="D3" t="n">
-        <v>93.37420643693173</v>
+        <v>15.17330854600141</v>
       </c>
       <c r="E3" t="n">
-        <v>18.01756697769656</v>
+        <v>2.927854633875691</v>
       </c>
       <c r="F3" t="n">
-        <v>17.97150031956095</v>
+        <v>2.920368801928654</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>24.35771648385096</v>
+        <v>3.958128928625781</v>
       </c>
       <c r="D4" t="n">
-        <v>24.61097535730197</v>
+        <v>3.999283495561571</v>
       </c>
       <c r="E4" t="n">
-        <v>18.01756697769656</v>
+        <v>2.927854633875691</v>
       </c>
       <c r="F4" t="n">
-        <v>17.97150031956095</v>
+        <v>2.920368801928654</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>55.59500834762772</v>
+        <v>9.034188856489505</v>
       </c>
       <c r="D5" t="n">
-        <v>54.96994390575931</v>
+        <v>8.932615884685887</v>
       </c>
       <c r="E5" t="n">
-        <v>18.01756697769656</v>
+        <v>2.927854633875691</v>
       </c>
       <c r="F5" t="n">
-        <v>17.97150031956095</v>
+        <v>2.920368801928654</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>47.08618601980127</v>
+        <v>7.651505228217706</v>
       </c>
       <c r="D6" t="n">
-        <v>46.43043919331774</v>
+        <v>7.544946368914133</v>
       </c>
       <c r="E6" t="n">
-        <v>18.01756697769656</v>
+        <v>2.927854633875691</v>
       </c>
       <c r="F6" t="n">
-        <v>17.97150031956095</v>
+        <v>2.920368801928654</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>52.92727837980495</v>
+        <v>8.600682736718303</v>
       </c>
       <c r="D7" t="n">
-        <v>52.48986525281386</v>
+        <v>8.529603103582252</v>
       </c>
       <c r="E7" t="n">
-        <v>18.01756697769656</v>
+        <v>2.927854633875691</v>
       </c>
       <c r="F7" t="n">
-        <v>17.97150031956095</v>
+        <v>2.920368801928654</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>41.45498521425419</v>
+        <v>6.736435097316306</v>
       </c>
       <c r="D8" t="n">
-        <v>41.7986692161502</v>
+        <v>6.792283747624408</v>
       </c>
       <c r="E8" t="n">
-        <v>18.01756697769656</v>
+        <v>2.927854633875691</v>
       </c>
       <c r="F8" t="n">
-        <v>17.97150031956095</v>
+        <v>2.920368801928654</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>43.9960517675007</v>
+        <v>7.149358412218863</v>
       </c>
       <c r="D9" t="n">
-        <v>43.36664177715043</v>
+        <v>7.047079288786945</v>
       </c>
       <c r="E9" t="n">
-        <v>18.01756697769656</v>
+        <v>2.927854633875691</v>
       </c>
       <c r="F9" t="n">
-        <v>17.97150031956095</v>
+        <v>2.920368801928654</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>49.00805651702555</v>
+        <v>7.963809184016652</v>
       </c>
       <c r="D10" t="n">
-        <v>48.72807315831013</v>
+        <v>7.918311888225396</v>
       </c>
       <c r="E10" t="n">
-        <v>18.01756697769656</v>
+        <v>2.927854633875691</v>
       </c>
       <c r="F10" t="n">
-        <v>17.97150031956095</v>
+        <v>2.920368801928654</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>42.59402863943015</v>
+        <v>6.9215296539074</v>
       </c>
       <c r="D11" t="n">
-        <v>42.22935253311045</v>
+        <v>6.862269786630448</v>
       </c>
       <c r="E11" t="n">
-        <v>18.01756697769656</v>
+        <v>2.927854633875691</v>
       </c>
       <c r="F11" t="n">
-        <v>17.97150031956095</v>
+        <v>2.920368801928654</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>27.62660056263342</v>
+        <v>4.48932259142793</v>
       </c>
       <c r="D12" t="n">
-        <v>27.81007816595089</v>
+        <v>4.51913770196702</v>
       </c>
       <c r="E12" t="n">
-        <v>18.01756697769656</v>
+        <v>2.927854633875691</v>
       </c>
       <c r="F12" t="n">
-        <v>17.97150031956095</v>
+        <v>2.920368801928654</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>32.83898613202598</v>
+        <v>5.336335246454222</v>
       </c>
       <c r="D13" t="n">
-        <v>32.39150109384104</v>
+        <v>5.263618927749168</v>
       </c>
       <c r="E13" t="n">
-        <v>18.01756697769656</v>
+        <v>2.927854633875691</v>
       </c>
       <c r="F13" t="n">
-        <v>17.97150031956095</v>
+        <v>2.920368801928654</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>36.80609906677979</v>
+        <v>5.980991098351716</v>
       </c>
       <c r="D14" t="n">
-        <v>36.97113472634864</v>
+        <v>6.007809393031653</v>
       </c>
       <c r="E14" t="n">
-        <v>18.01756697769656</v>
+        <v>2.927854633875691</v>
       </c>
       <c r="F14" t="n">
-        <v>17.97150031956095</v>
+        <v>2.920368801928654</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>18.44851244514164</v>
+        <v>2.997883272335516</v>
       </c>
       <c r="D15" t="n">
-        <v>17.82355972489161</v>
+        <v>2.896328455294886</v>
       </c>
       <c r="E15" t="n">
-        <v>18.01756697769656</v>
+        <v>2.927854633875691</v>
       </c>
       <c r="F15" t="n">
-        <v>17.97150031956095</v>
+        <v>2.920368801928654</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>34.7564408853039</v>
+        <v>5.647921643861884</v>
       </c>
       <c r="D16" t="n">
-        <v>34.86907849343059</v>
+        <v>5.666225255182471</v>
       </c>
       <c r="E16" t="n">
-        <v>18.01756697769656</v>
+        <v>2.927854633875691</v>
       </c>
       <c r="F16" t="n">
-        <v>17.97150031956095</v>
+        <v>2.920368801928654</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>18.42550428531523</v>
+        <v>2.994144446363725</v>
       </c>
       <c r="D17" t="n">
-        <v>18.2625193877864</v>
+        <v>2.967659400515291</v>
       </c>
       <c r="E17" t="n">
-        <v>18.01756697769656</v>
+        <v>2.927854633875691</v>
       </c>
       <c r="F17" t="n">
-        <v>17.97150031956095</v>
+        <v>2.920368801928654</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>32.85779411494292</v>
+        <v>5.339391543678224</v>
       </c>
       <c r="D18" t="n">
-        <v>32.66298263884794</v>
+        <v>5.30773467881279</v>
       </c>
       <c r="E18" t="n">
-        <v>18.01756697769656</v>
+        <v>2.927854633875691</v>
       </c>
       <c r="F18" t="n">
-        <v>17.97150031956095</v>
+        <v>2.920368801928654</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1024,16 +1024,16 @@
         <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>60.5474466791598</v>
+        <v>9.838960085363468</v>
       </c>
       <c r="D19" t="n">
-        <v>60.74890843468739</v>
+        <v>9.8716976206367</v>
       </c>
       <c r="E19" t="n">
-        <v>18.01756697769656</v>
+        <v>2.927854633875691</v>
       </c>
       <c r="F19" t="n">
-        <v>17.97150031956095</v>
+        <v>2.920368801928654</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1056,16 +1056,16 @@
         <v>19</v>
       </c>
       <c r="C20" t="n">
-        <v>14.36436458980563</v>
+        <v>2.334209245843415</v>
       </c>
       <c r="D20" t="n">
-        <v>14.79175982668958</v>
+        <v>2.403660971837057</v>
       </c>
       <c r="E20" t="n">
-        <v>18.01756697769656</v>
+        <v>2.927854633875691</v>
       </c>
       <c r="F20" t="n">
-        <v>17.97150031956095</v>
+        <v>2.920368801928654</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1088,16 +1088,16 @@
         <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>25.71665983379397</v>
+        <v>4.178957222991521</v>
       </c>
       <c r="D21" t="n">
-        <v>25.9516698115787</v>
+        <v>4.21714634438154</v>
       </c>
       <c r="E21" t="n">
-        <v>18.01756697769656</v>
+        <v>2.927854633875691</v>
       </c>
       <c r="F21" t="n">
-        <v>17.97150031956095</v>
+        <v>2.920368801928654</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1120,16 +1120,16 @@
         <v>21</v>
       </c>
       <c r="C22" t="n">
-        <v>46.08986992567053</v>
+        <v>7.489603862921462</v>
       </c>
       <c r="D22" t="n">
-        <v>46.17674419038526</v>
+        <v>7.503720930937606</v>
       </c>
       <c r="E22" t="n">
-        <v>18.01756697769656</v>
+        <v>2.927854633875691</v>
       </c>
       <c r="F22" t="n">
-        <v>17.97150031956095</v>
+        <v>2.920368801928654</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1152,16 +1152,16 @@
         <v>22</v>
       </c>
       <c r="C23" t="n">
-        <v>28.52260870945285</v>
+        <v>4.634923915286089</v>
       </c>
       <c r="D23" t="n">
-        <v>29.17043324060877</v>
+        <v>4.740195401598926</v>
       </c>
       <c r="E23" t="n">
-        <v>18.01756697769656</v>
+        <v>2.927854633875691</v>
       </c>
       <c r="F23" t="n">
-        <v>17.97150031956095</v>
+        <v>2.920368801928654</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1184,16 +1184,16 @@
         <v>23</v>
       </c>
       <c r="C24" t="n">
-        <v>75.71606969719309</v>
+        <v>12.30386132579388</v>
       </c>
       <c r="D24" t="n">
-        <v>75.85335024288734</v>
+        <v>12.32616941446919</v>
       </c>
       <c r="E24" t="n">
-        <v>18.01756697769656</v>
+        <v>2.927854633875691</v>
       </c>
       <c r="F24" t="n">
-        <v>17.97150031956095</v>
+        <v>2.920368801928654</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1216,16 +1216,16 @@
         <v>24</v>
       </c>
       <c r="C25" t="n">
-        <v>40.55937586458479</v>
+        <v>6.590898577995028</v>
       </c>
       <c r="D25" t="n">
-        <v>41.13601175037726</v>
+        <v>6.684601909436305</v>
       </c>
       <c r="E25" t="n">
-        <v>18.01756697769656</v>
+        <v>2.927854633875691</v>
       </c>
       <c r="F25" t="n">
-        <v>17.97150031956095</v>
+        <v>2.920368801928654</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1248,16 +1248,16 @@
         <v>25</v>
       </c>
       <c r="C26" t="n">
-        <v>51.3839391898362</v>
+        <v>8.349890118348382</v>
       </c>
       <c r="D26" t="n">
-        <v>51.98750690849468</v>
+        <v>8.447969872630386</v>
       </c>
       <c r="E26" t="n">
-        <v>18.01756697769656</v>
+        <v>2.927854633875691</v>
       </c>
       <c r="F26" t="n">
-        <v>17.97150031956095</v>
+        <v>2.920368801928654</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1280,16 +1280,16 @@
         <v>26</v>
       </c>
       <c r="C27" t="n">
-        <v>65.00783894281817</v>
+        <v>10.56377382820795</v>
       </c>
       <c r="D27" t="n">
-        <v>65.27155213650296</v>
+        <v>10.60662722218173</v>
       </c>
       <c r="E27" t="n">
-        <v>18.01756697769656</v>
+        <v>2.927854633875691</v>
       </c>
       <c r="F27" t="n">
-        <v>17.97150031956095</v>
+        <v>2.920368801928654</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1312,16 +1312,16 @@
         <v>27</v>
       </c>
       <c r="C28" t="n">
-        <v>63.99243525204924</v>
+        <v>10.398770728458</v>
       </c>
       <c r="D28" t="n">
-        <v>64.62337637050834</v>
+        <v>10.50129866020761</v>
       </c>
       <c r="E28" t="n">
-        <v>18.01756697769656</v>
+        <v>2.927854633875691</v>
       </c>
       <c r="F28" t="n">
-        <v>17.97150031956095</v>
+        <v>2.920368801928654</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
